--- a/data/trans_orig/P6705-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6705-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2012</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2012 (tasa de respuesta: 99,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53872</t>
+          <t>52269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82545</t>
+          <t>83233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84377</t>
+          <t>85537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120330</t>
+          <t>121651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59235</t>
+          <t>60371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>50471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69541</t>
+          <t>67698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>101215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>58129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>86485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>92117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130116</t>
+          <t>128472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>64318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>39500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64441</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96853</t>
+          <t>97217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>38435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>64995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>64990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>98057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>78272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123763</t>
+          <t>123683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169138</t>
+          <t>167564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>60007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123725</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93202</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129434</t>
+          <t>130661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57026</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>89484</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>159812</t>
+          <t>159751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>207957</t>
+          <t>207141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70743</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106482</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54973</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107421</t>
+          <t>107555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151360</t>
+          <t>153071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87660</t>
+          <t>89352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36696</t>
+          <t>35944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61525</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100883</t>
+          <t>100322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142848</t>
+          <t>137958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70186</t>
+          <t>69874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57499</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79246</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116658</t>
+          <t>116812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59476</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>38983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55076</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69132</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104159</t>
+          <t>103855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66034</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>119949</t>
+          <t>116425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162962</t>
+          <t>158980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45225</t>
+          <t>44356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75835</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81673</t>
+          <t>80796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118225</t>
+          <t>116183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>62168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95386</t>
+          <t>93766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39583</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>68683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>109521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152577</t>
+          <t>151781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58464</t>
+          <t>58849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90854</t>
+          <t>90831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54155</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>82946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121615</t>
+          <t>121445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164105</t>
+          <t>166826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>53547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>83223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56770</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>92308</t>
+          <t>93524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>130894</t>
+          <t>132874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123383</t>
+          <t>120962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161984</t>
+          <t>160438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64095</t>
+          <t>65027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93327</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194451</t>
+          <t>195230</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>240689</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64819</t>
+          <t>64996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98210</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77206</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119191</t>
+          <t>121572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162832</t>
+          <t>165112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43366</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71549</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62472</t>
+          <t>62558</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>84193</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>125031</t>
+          <t>122488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>246925</t>
+          <t>245727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>307856</t>
+          <t>308436</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>183408</t>
+          <t>185104</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>237466</t>
+          <t>238914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>444025</t>
+          <t>448265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>526778</t>
+          <t>529472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>187232</t>
+          <t>189520</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>244207</t>
+          <t>245821</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>132934</t>
+          <t>131715</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178667</t>
+          <t>178807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>338479</t>
+          <t>340094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>408595</t>
+          <t>415117</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>375891</t>
+          <t>374773</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>447961</t>
+          <t>446883</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>216332</t>
+          <t>214590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>271841</t>
+          <t>271387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>606009</t>
+          <t>605221</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>696722</t>
+          <t>695710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>249247</t>
+          <t>246614</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>308489</t>
+          <t>311365</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146213</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>194595</t>
+          <t>196785</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>409947</t>
+          <t>409349</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>486863</t>
+          <t>492050</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>206399</t>
+          <t>208043</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>262543</t>
+          <t>263891</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>194873</t>
+          <t>195300</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>362680</t>
+          <t>365555</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>441352</t>
+          <t>442629</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2016</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>42801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69119</t>
+          <t>68639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77074</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111047</t>
+          <t>109939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61029</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65627</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98146</t>
+          <t>98097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52266</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>82334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>39772</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100917</t>
+          <t>99306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138355</t>
+          <t>136906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>61099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>41525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94655</t>
+          <t>95573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23516</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56405</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101426</t>
+          <t>100393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140602</t>
+          <t>136789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>83666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164219</t>
+          <t>163846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212850</t>
+          <t>210175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>66882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102660</t>
+          <t>101971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48365</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>73110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122854</t>
+          <t>121402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167194</t>
+          <t>168227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85656</t>
+          <t>86753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124479</t>
+          <t>124068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76479</t>
+          <t>77405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144906</t>
+          <t>144487</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191072</t>
+          <t>190224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81118</t>
+          <t>79402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52734</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83883</t>
+          <t>86189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123592</t>
+          <t>126945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55317</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>103621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57792</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88953</t>
+          <t>90294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60844</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100931</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>141570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54327</t>
+          <t>55147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86451</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69993</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106762</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147222</t>
+          <t>146195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109922</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150178</t>
+          <t>148507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77340</t>
+          <t>76502</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108363</t>
+          <t>108854</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194883</t>
+          <t>194730</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>244589</t>
+          <t>243084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50045</t>
+          <t>49790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80186</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57582</t>
+          <t>58791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88784</t>
+          <t>89499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126593</t>
+          <t>127331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42064</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77244</t>
+          <t>77668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95782</t>
+          <t>94804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132045</t>
+          <t>131577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63897</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95735</t>
+          <t>92947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168306</t>
+          <t>165051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213677</t>
+          <t>213111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56449</t>
+          <t>54009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70203</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108513</t>
+          <t>108973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149232</t>
+          <t>151977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>90149</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124385</t>
+          <t>126502</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63598</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93728</t>
+          <t>95777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>160730</t>
+          <t>162421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>206361</t>
+          <t>207879</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80794</t>
+          <t>82371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53046</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81732</t>
+          <t>81307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112751</t>
+          <t>114204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153129</t>
+          <t>154911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61120</t>
+          <t>62088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73668</t>
+          <t>73580</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111976</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>327522</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>394086</t>
+          <t>393856</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207037</t>
+          <t>204245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>260989</t>
+          <t>257559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>545261</t>
+          <t>544971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>632350</t>
+          <t>635633</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>243109</t>
+          <t>241052</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>301409</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>182894</t>
+          <t>181282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>234819</t>
+          <t>233899</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>436265</t>
+          <t>437650</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>517444</t>
+          <t>516739</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>370713</t>
+          <t>375344</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>443706</t>
+          <t>443476</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>254467</t>
+          <t>253697</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>313145</t>
+          <t>314397</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>644271</t>
+          <t>646581</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>733387</t>
+          <t>737326</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>211262</t>
+          <t>211360</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>266890</t>
+          <t>268993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157723</t>
+          <t>156924</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>208404</t>
+          <t>209126</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>386456</t>
+          <t>384849</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>460210</t>
+          <t>461637</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>122771</t>
+          <t>124050</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>170460</t>
+          <t>172209</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>113599</t>
+          <t>113946</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>156222</t>
+          <t>155817</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>246848</t>
+          <t>248636</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>314058</t>
+          <t>316144</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2023</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>31182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58434</t>
+          <t>59417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35701</t>
+          <t>34906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>63715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34061</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81086</t>
+          <t>81868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>361029</t>
+          <t>359357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>440590</t>
+          <t>440615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111279</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38209</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137628</t>
+          <t>138863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116451</t>
+          <t>118855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43808</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156306</t>
+          <t>155363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80346</t>
+          <t>84728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98917</t>
+          <t>98228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38584</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53520</t>
+          <t>52815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32838</t>
+          <t>32262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44151</t>
+          <t>44856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>76570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>30541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>194689</t>
+          <t>192027</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>551967</t>
+          <t>551285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>121871</t>
+          <t>123304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>299528</t>
+          <t>301313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>746801</t>
+          <t>777287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>70512</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70975</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>196239</t>
+          <t>193413</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>200842</t>
+          <t>195985</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96357</t>
+          <t>95994</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126872</t>
+          <t>125218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>115262</t>
+          <t>106631</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>314196</t>
+          <t>312525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>96432</t>
+          <t>94367</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60572</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>46104</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>143840</t>
+          <t>145642</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>67016</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6705-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6705-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52269</t>
+          <t>53142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>82443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85537</t>
+          <t>84972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121651</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34814</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>59270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>49621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67698</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101215</t>
+          <t>102591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58129</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86485</t>
+          <t>87374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50303</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92117</t>
+          <t>93323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>130552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64318</t>
+          <t>64975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64641</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97217</t>
+          <t>95554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38435</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64990</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98057</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>80421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123683</t>
+          <t>123342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167564</t>
+          <t>167913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>34064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>59876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86196</t>
+          <t>84612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123445</t>
+          <t>123940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>91833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130661</t>
+          <t>129798</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59031</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89484</t>
+          <t>88031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>159751</t>
+          <t>159705</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>207141</t>
+          <t>205996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105702</t>
+          <t>106814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29714</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107555</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153071</t>
+          <t>148088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>57500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89352</t>
+          <t>89265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>61409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137958</t>
+          <t>141534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>41970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69874</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>29871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>54697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116812</t>
+          <t>117906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>58929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38983</t>
+          <t>39893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57499</t>
+          <t>57710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91505</t>
+          <t>92238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69469</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103855</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116425</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158980</t>
+          <t>162066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>74726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>51862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80796</t>
+          <t>80881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116183</t>
+          <t>118760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>61169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93766</t>
+          <t>92352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>39967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68683</t>
+          <t>68407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109521</t>
+          <t>108662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151781</t>
+          <t>149527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90831</t>
+          <t>90855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82946</t>
+          <t>83558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>119843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166826</t>
+          <t>165142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53547</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83223</t>
+          <t>84498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93524</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132874</t>
+          <t>133208</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120962</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160438</t>
+          <t>161074</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>64679</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>96326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>195230</t>
+          <t>195576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>247430</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64996</t>
+          <t>63150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96410</t>
+          <t>97370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121572</t>
+          <t>122098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165112</t>
+          <t>163911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69804</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62558</t>
+          <t>62671</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122488</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>245727</t>
+          <t>248919</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>308436</t>
+          <t>311306</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185104</t>
+          <t>185698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>237904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>448265</t>
+          <t>446847</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>529472</t>
+          <t>530487</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>189520</t>
+          <t>190249</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>244108</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131715</t>
+          <t>134227</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178807</t>
+          <t>182991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>340094</t>
+          <t>338213</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>415117</t>
+          <t>408749</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>374773</t>
+          <t>375739</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>446883</t>
+          <t>448309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>214590</t>
+          <t>215316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>271387</t>
+          <t>273997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>605221</t>
+          <t>609750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>695710</t>
+          <t>696577</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>246243</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>311365</t>
+          <t>308205</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>147401</t>
+          <t>146992</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>196785</t>
+          <t>196152</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>409349</t>
+          <t>408388</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>492050</t>
+          <t>487252</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>208043</t>
+          <t>205416</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>263891</t>
+          <t>262380</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>147360</t>
+          <t>145996</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>195300</t>
+          <t>194583</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>365555</t>
+          <t>364326</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>442629</t>
+          <t>442163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68639</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>27549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>48339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77174</t>
+          <t>77110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109939</t>
+          <t>110581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>35118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60626</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64743</t>
+          <t>64575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>97844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51976</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82334</t>
+          <t>84470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136906</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61099</t>
+          <t>59890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41525</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>39561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100393</t>
+          <t>99846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136789</t>
+          <t>137354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55791</t>
+          <t>54977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83666</t>
+          <t>81912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163846</t>
+          <t>163252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210175</t>
+          <t>212771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66882</t>
+          <t>65774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>100767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73110</t>
+          <t>75595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168227</t>
+          <t>166919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86753</t>
+          <t>86299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124068</t>
+          <t>124264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48843</t>
+          <t>49555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77405</t>
+          <t>77055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144487</t>
+          <t>143034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>190224</t>
+          <t>191117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>49310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79402</t>
+          <t>81158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86189</t>
+          <t>86634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126945</t>
+          <t>126318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31579</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58437</t>
+          <t>57037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>31097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55825</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68753</t>
+          <t>70451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103621</t>
+          <t>104761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58911</t>
+          <t>57461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>89245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t>101067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141570</t>
+          <t>141615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>88269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69866</t>
+          <t>71585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105918</t>
+          <t>105973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146195</t>
+          <t>147266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111403</t>
+          <t>109770</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148507</t>
+          <t>148077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76502</t>
+          <t>76100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108854</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194730</t>
+          <t>195001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243084</t>
+          <t>244092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>49576</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79207</t>
+          <t>77638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58791</t>
+          <t>57857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127331</t>
+          <t>126091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40814</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44731</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77668</t>
+          <t>76978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94804</t>
+          <t>95492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131577</t>
+          <t>130488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92947</t>
+          <t>94578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165051</t>
+          <t>169202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213111</t>
+          <t>214415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86339</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>42900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>70351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108973</t>
+          <t>107757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>151977</t>
+          <t>146816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90149</t>
+          <t>88837</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126502</t>
+          <t>123397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95777</t>
+          <t>95111</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>162421</t>
+          <t>157655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>207879</t>
+          <t>207701</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53353</t>
+          <t>52986</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82371</t>
+          <t>82229</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81307</t>
+          <t>83721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114204</t>
+          <t>112390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154911</t>
+          <t>154220</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>62251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>33350</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113328</t>
+          <t>110717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>326370</t>
+          <t>324492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>393856</t>
+          <t>392037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>204245</t>
+          <t>207648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>257559</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>544971</t>
+          <t>550183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>635633</t>
+          <t>634688</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>241052</t>
+          <t>237920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>303326</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>181282</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>233899</t>
+          <t>235183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>437650</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>516739</t>
+          <t>522940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>375344</t>
+          <t>371930</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>443476</t>
+          <t>440804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>253697</t>
+          <t>255493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>314397</t>
+          <t>312772</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>646581</t>
+          <t>644048</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>737326</t>
+          <t>736583</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>211360</t>
+          <t>214534</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>268993</t>
+          <t>274768</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156924</t>
+          <t>158500</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>209126</t>
+          <t>205968</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>384849</t>
+          <t>379925</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461637</t>
+          <t>459213</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>123116</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>172209</t>
+          <t>171747</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>113946</t>
+          <t>113231</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>155817</t>
+          <t>156153</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>248636</t>
+          <t>243297</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>316144</t>
+          <t>312256</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42982</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>65584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38334</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23178</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>50247</t>
+          <t>55254</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63715</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>279249</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81868</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359357</t>
+          <t>50639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>34020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>300379</t>
+          <t>62277</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96939</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>440615</t>
+          <t>78558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38832</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108504</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>32542</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68194</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138863</t>
+          <t>91881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>39522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118855</t>
+          <t>67185</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>37312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>75986</t>
+          <t>89428</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>73885</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155363</t>
+          <t>104875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84728</t>
+          <t>43482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>21388</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47437</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98228</t>
+          <t>67143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>32572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>49332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>35194</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>71093</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72136</t>
+          <t>87385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41955</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32900</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36070</t>
+          <t>39792</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78025</t>
+          <t>86344</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>73458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90510</t>
+          <t>101475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>22451</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44856</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36556</t>
+          <t>40225</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>65034</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76570</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>23584</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>373842</t>
+          <t>145412</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>192027</t>
+          <t>125726</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>551285</t>
+          <t>170667</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>107384</t>
+          <t>122383</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>105482</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123304</t>
+          <t>139000</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>481226</t>
+          <t>267795</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>301313</t>
+          <t>239231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>777287</t>
+          <t>299502</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>94254</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32328</t>
+          <t>75215</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>116980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>57487</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47039</t>
+          <t>52754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70512</t>
+          <t>78708</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>141284</t>
+          <t>158591</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>63881</t>
+          <t>133918</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>193413</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119200</t>
+          <t>135329</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195985</t>
+          <t>157310</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>110688</t>
+          <t>120311</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95994</t>
+          <t>104656</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125218</t>
+          <t>136209</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>229888</t>
+          <t>255640</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>230411</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>312525</t>
+          <t>285815</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62531</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>94367</t>
+          <t>80334</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>41933</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>67803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>103597</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46104</t>
+          <t>98088</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>145642</t>
+          <t>139274</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67016</t>
+          <t>58919</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>75865</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>59238</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>95383</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
